--- a/data/trans_dic/P13_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,65</t>
+          <t>2,65; 6,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,05</t>
+          <t>2,16; 6,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,99</t>
+          <t>1,93; 5,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,65</t>
+          <t>2,99; 6,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,32</t>
+          <t>3,02; 8,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,42</t>
+          <t>1,97; 6,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,04</t>
+          <t>2,3; 7,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,24</t>
+          <t>2,56; 5,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,32</t>
+          <t>3,4; 6,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,38</t>
+          <t>2,59; 5,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,56</t>
+          <t>2,53; 5,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,63</t>
+          <t>3,15; 5,46</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,47</t>
+          <t>0,44; 3,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,75</t>
+          <t>2,43; 6,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,87</t>
+          <t>1,57; 5,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,21</t>
+          <t>2,12; 5,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,83</t>
+          <t>1,11; 4,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,52</t>
+          <t>3,51; 9,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,21</t>
+          <t>0,89; 4,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,46</t>
+          <t>2,99; 6,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,24</t>
+          <t>0,99; 3,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,99</t>
+          <t>3,5; 6,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,03</t>
+          <t>1,53; 3,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,44</t>
+          <t>2,97; 5,36</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,38</t>
+          <t>0,93; 3,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,76</t>
+          <t>3,74; 7,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,5</t>
+          <t>2,38; 6,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,94</t>
+          <t>1,11; 6,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 13,0</t>
+          <t>3,82; 13,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,04</t>
+          <t>5,93; 13,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 14,14</t>
+          <t>5,36; 14,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 15,49</t>
+          <t>7,91; 14,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,76</t>
+          <t>2,04; 4,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,38</t>
+          <t>4,89; 8,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,36</t>
+          <t>3,68; 7,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,68</t>
+          <t>1,79; 7,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,86</t>
+          <t>2,73; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,62</t>
+          <t>3,9; 6,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,63</t>
+          <t>2,34; 4,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,91</t>
+          <t>4,95; 7,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,8</t>
+          <t>3,44; 6,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,85</t>
+          <t>5,86; 9,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,31</t>
+          <t>4,66; 8,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,84</t>
+          <t>2,67; 6,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,12</t>
+          <t>3,23; 5,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,31</t>
+          <t>5,03; 7,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,61</t>
+          <t>3,58; 5,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 6,86</t>
+          <t>3,92; 6,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,31</t>
+          <t>2,88; 7,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,63</t>
+          <t>2,33; 5,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,73</t>
+          <t>3,18; 6,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,33</t>
+          <t>5,2; 10,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,94</t>
+          <t>2,59; 5,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,3</t>
+          <t>10,05; 15,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,53</t>
+          <t>4,74; 8,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,76</t>
+          <t>6,4; 10,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,86</t>
+          <t>3,07; 5,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,63</t>
+          <t>7,35; 10,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,28</t>
+          <t>4,49; 6,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 9,88</t>
+          <t>6,66; 9,91</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,11</t>
+          <t>1,02; 4,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,85</t>
+          <t>2,47; 8,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,79</t>
+          <t>0,65; 4,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,95</t>
+          <t>4,25; 6,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,32</t>
+          <t>9,18; 13,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,04</t>
+          <t>4,19; 7,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 10,57</t>
+          <t>7,53; 10,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,26</t>
+          <t>3,92; 6,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,4</t>
+          <t>8,04; 11,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,81</t>
+          <t>3,44; 5,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,61</t>
+          <t>6,03; 8,65</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,85</t>
+          <t>2,58; 3,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 5,5</t>
+          <t>3,9; 5,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,18</t>
+          <t>2,88; 4,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,76</t>
+          <t>3,78; 5,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,67</t>
+          <t>4,12; 5,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,35; 10,39</t>
+          <t>8,41; 10,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,33</t>
+          <t>4,76; 6,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,57</t>
+          <t>5,55; 7,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,53</t>
+          <t>3,56; 4,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 7,66</t>
+          <t>6,42; 7,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,07</t>
+          <t>4,02; 5,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,57</t>
+          <t>5,09; 6,54</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11996; 31491</t>
+          <t>12550; 32083</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9273; 26374</t>
+          <t>9441; 28227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9134; 25637</t>
+          <t>8279; 25008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14872; 33591</t>
+          <t>15122; 34954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9624; 25503</t>
+          <t>9268; 26359</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6780; 20189</t>
+          <t>6190; 19416</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8358; 24316</t>
+          <t>7935; 24630</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11053; 23445</t>
+          <t>11475; 24178</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25809; 49355</t>
+          <t>26554; 51850</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18504; 40376</t>
+          <t>19452; 39793</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20388; 42963</t>
+          <t>19545; 42351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30461; 53645</t>
+          <t>29994; 52046</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1593; 12715</t>
+          <t>1633; 12558</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10089; 28266</t>
+          <t>10160; 28295</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5917; 18387</t>
+          <t>5935; 19409</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9573; 23564</t>
+          <t>9596; 23861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4215; 17956</t>
+          <t>4122; 16702</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11340; 32172</t>
+          <t>11848; 32090</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3383; 15667</t>
+          <t>3297; 15643</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11030; 24696</t>
+          <t>11440; 24840</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7511; 23926</t>
+          <t>7321; 23368</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26498; 52912</t>
+          <t>26494; 52286</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12112; 30202</t>
+          <t>11445; 29436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24168; 45406</t>
+          <t>24756; 44782</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5048; 18341</t>
+          <t>5043; 17633</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23448; 48825</t>
+          <t>23538; 47457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13534; 33903</t>
+          <t>12439; 32402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7908; 39669</t>
+          <t>7394; 40950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6314; 21814</t>
+          <t>6417; 22049</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15850; 33922</t>
+          <t>15419; 34732</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8459; 23482</t>
+          <t>8910; 24566</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12948; 25781</t>
+          <t>13167; 24926</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14418; 33824</t>
+          <t>14459; 33693</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43931; 74538</t>
+          <t>43528; 73317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25775; 50610</t>
+          <t>25322; 49567</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16049; 64008</t>
+          <t>14920; 64188</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33144; 60169</t>
+          <t>33771; 59427</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44247; 76568</t>
+          <t>45098; 77115</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26420; 53259</t>
+          <t>26861; 54571</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53094; 81849</t>
+          <t>51274; 82722</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24718; 48551</t>
+          <t>24596; 47917</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44242; 75298</t>
+          <t>44792; 75965</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38485; 68490</t>
+          <t>38389; 67901</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24202; 66857</t>
+          <t>26110; 68203</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64433; 100052</t>
+          <t>63047; 97914</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98274; 140418</t>
+          <t>96709; 142095</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71200; 110783</t>
+          <t>70754; 111322</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82302; 138094</t>
+          <t>78887; 136666</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10298; 25641</t>
+          <t>10079; 26622</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12208; 28736</t>
+          <t>11890; 28750</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21114; 41765</t>
+          <t>19759; 41346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25195; 48855</t>
+          <t>24599; 47645</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14161; 33791</t>
+          <t>14731; 33343</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77608; 116543</t>
+          <t>76538; 115394</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35081; 62943</t>
+          <t>35014; 62098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55774; 90309</t>
+          <t>53695; 88571</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28528; 53835</t>
+          <t>28239; 53375</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93134; 135173</t>
+          <t>93453; 134129</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62419; 98930</t>
+          <t>61043; 94441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89261; 129665</t>
+          <t>87465; 130104</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3001; 15229</t>
+          <t>3040; 14895</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6351; 20940</t>
+          <t>6595; 21598</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6644</t>
+          <t>0; 6279</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1670; 9117</t>
+          <t>1566; 9880</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53701; 86747</t>
+          <t>53027; 86530</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100528; 147564</t>
+          <t>101774; 145358</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44049; 76040</t>
+          <t>45284; 76005</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55677; 80220</t>
+          <t>57165; 82538</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60356; 96808</t>
+          <t>60620; 93923</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110679; 156723</t>
+          <t>110552; 155869</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46413; 79474</t>
+          <t>47080; 78563</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59666; 86088</t>
+          <t>60266; 86464</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>86145; 125758</t>
+          <t>84314; 127878</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>135340; 187889</t>
+          <t>133317; 184393</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97255; 141572</t>
+          <t>97605; 141694</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129053; 194249</t>
+          <t>127502; 195970</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>138413; 191500</t>
+          <t>139325; 191573</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>296101; 368479</t>
+          <t>298251; 365354</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>167192; 223406</t>
+          <t>167917; 225040</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>196109; 270554</t>
+          <t>198312; 271434</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>237065; 300964</t>
+          <t>236663; 301408</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>447897; 533501</t>
+          <t>447291; 534516</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>277629; 350725</t>
+          <t>277983; 348591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>349026; 456159</t>
+          <t>353231; 454240</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,77</t>
+          <t>2,69; 6,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,47</t>
+          <t>2,04; 5,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,84</t>
+          <t>1,92; 5,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,92</t>
+          <t>2,88; 6,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 8,6</t>
+          <t>3,23; 8,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,17</t>
+          <t>2,19; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,14</t>
+          <t>2,38; 7,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,4</t>
+          <t>2,71; 5,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,64</t>
+          <t>3,32; 6,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,3</t>
+          <t>2,39; 5,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,48</t>
+          <t>2,55; 5,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,46</t>
+          <t>3,19; 5,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,42</t>
+          <t>0,43; 3,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,76</t>
+          <t>2,47; 6,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,15</t>
+          <t>1,59; 5,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,28</t>
+          <t>2,01; 5,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,49</t>
+          <t>1,08; 4,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,49</t>
+          <t>3,49; 9,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,2</t>
+          <t>0,87; 4,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,49</t>
+          <t>2,9; 6,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,16</t>
+          <t>1,04; 3,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,91</t>
+          <t>3,43; 6,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,93</t>
+          <t>1,66; 3,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,36</t>
+          <t>2,82; 5,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,25</t>
+          <t>0,88; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,54</t>
+          <t>3,72; 7,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,21</t>
+          <t>2,57; 6,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,14</t>
+          <t>3,57; 8,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 13,14</t>
+          <t>3,84; 12,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,35</t>
+          <t>5,89; 13,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,79</t>
+          <t>4,81; 14,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 14,97</t>
+          <t>7,38; 14,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,74</t>
+          <t>2,03; 4,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,24</t>
+          <t>4,84; 8,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,2</t>
+          <t>3,64; 7,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,7</t>
+          <t>5,24; 9,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,8</t>
+          <t>2,64; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,67</t>
+          <t>3,95; 6,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,75</t>
+          <t>2,31; 4,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,99</t>
+          <t>5,25; 8,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,71</t>
+          <t>3,32; 6,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,93</t>
+          <t>5,83; 9,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,24</t>
+          <t>4,61; 8,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,97</t>
+          <t>4,96; 7,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,01</t>
+          <t>3,21; 5,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 7,39</t>
+          <t>5,05; 7,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,64</t>
+          <t>3,6; 5,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,79</t>
+          <t>5,48; 7,66</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,59</t>
+          <t>2,86; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,63</t>
+          <t>2,39; 5,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,66</t>
+          <t>3,42; 6,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,07</t>
+          <t>4,69; 8,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,86</t>
+          <t>2,42; 5,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,15</t>
+          <t>9,92; 14,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,41</t>
+          <t>4,71; 8,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,55</t>
+          <t>8,6; 11,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,81</t>
+          <t>3,06; 5,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,54</t>
+          <t>7,33; 10,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,95</t>
+          <t>4,51; 7,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 9,91</t>
+          <t>7,37; 9,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,99</t>
+          <t>1,07; 5,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,09</t>
+          <t>2,31; 8,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,11</t>
+          <t>0,8; 4,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,93</t>
+          <t>4,26; 6,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 13,12</t>
+          <t>9,23; 13,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,03</t>
+          <t>4,12; 7,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 10,87</t>
+          <t>7,43; 10,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,07</t>
+          <t>3,93; 6,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,33</t>
+          <t>8,25; 11,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,74</t>
+          <t>3,4; 5,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 8,65</t>
+          <t>6,07; 8,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,91</t>
+          <t>2,58; 3,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,39</t>
+          <t>3,94; 5,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,19</t>
+          <t>2,89; 4,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,81</t>
+          <t>4,6; 6,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,67</t>
+          <t>4,16; 5,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 10,3</t>
+          <t>8,35; 10,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,6</t>
+          <t>6,75; 8,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,53</t>
+          <t>3,57; 4,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,67</t>
+          <t>6,39; 7,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,04</t>
+          <t>4,04; 5,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,54</t>
+          <t>5,88; 6,85</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>44327</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12550; 32083</t>
+          <t>12763; 30312</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9441; 28227</t>
+          <t>8918; 25636</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8279; 25008</t>
+          <t>8236; 24642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15122; 34954</t>
+          <t>15843; 36719</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9268; 26359</t>
+          <t>9913; 25655</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6190; 19416</t>
+          <t>6887; 21033</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7935; 24630</t>
+          <t>8228; 24981</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11475; 24178</t>
+          <t>13213; 27672</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26554; 51850</t>
+          <t>25897; 51945</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19452; 39793</t>
+          <t>17934; 40746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19545; 42351</t>
+          <t>19746; 42726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29994; 52046</t>
+          <t>33098; 57757</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>34804</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1633; 12558</t>
+          <t>1590; 13515</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10160; 28295</t>
+          <t>10343; 27149</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5935; 19409</t>
+          <t>6015; 19463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9596; 23861</t>
+          <t>9723; 25130</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4122; 16702</t>
+          <t>4005; 17552</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11848; 32090</t>
+          <t>11780; 31098</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3297; 15643</t>
+          <t>3228; 16090</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11440; 24840</t>
+          <t>12268; 27799</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7321; 23368</t>
+          <t>7700; 23255</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26494; 52286</t>
+          <t>25965; 52182</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11445; 29436</t>
+          <t>12464; 29467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24756; 44782</t>
+          <t>25534; 46534</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>45120</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5043; 17633</t>
+          <t>4799; 18132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23538; 47457</t>
+          <t>23407; 48507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12439; 32402</t>
+          <t>13418; 33290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7394; 40950</t>
+          <t>16808; 39076</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6417; 22049</t>
+          <t>6442; 20559</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15419; 34732</t>
+          <t>15318; 35078</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8910; 24566</t>
+          <t>7984; 24699</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13167; 24926</t>
+          <t>13794; 27617</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14459; 33693</t>
+          <t>14415; 34176</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43528; 73317</t>
+          <t>43081; 74839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25322; 49567</t>
+          <t>25071; 49849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14920; 64188</t>
+          <t>34474; 60076</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48608</t>
+          <t>53873</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>114231</t>
+          <t>128592</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33771; 59427</t>
+          <t>32754; 59502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45098; 77115</t>
+          <t>45727; 76819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26861; 54571</t>
+          <t>26573; 51250</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51274; 82722</t>
+          <t>59431; 95223</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24596; 47917</t>
+          <t>23713; 48114</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44792; 75965</t>
+          <t>44595; 75872</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38389; 67901</t>
+          <t>37991; 66331</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26110; 68203</t>
+          <t>42689; 66894</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63047; 97914</t>
+          <t>62772; 99806</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>96709; 142095</t>
+          <t>96977; 142867</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70754; 111322</t>
+          <t>70976; 110878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78887; 136666</t>
+          <t>109211; 152610</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>83394</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>109442</t>
+          <t>120283</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10079; 26622</t>
+          <t>10011; 26804</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11890; 28750</t>
+          <t>12183; 29675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19759; 41346</t>
+          <t>21231; 40416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24599; 47645</t>
+          <t>26553; 49945</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14731; 33343</t>
+          <t>13758; 32514</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76538; 115394</t>
+          <t>75548; 112025</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35014; 62098</t>
+          <t>34755; 62492</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53695; 88571</t>
+          <t>71292; 97970</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28239; 53375</t>
+          <t>28176; 53814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93453; 134129</t>
+          <t>93267; 136552</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61043; 94441</t>
+          <t>61301; 96276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87465; 130104</t>
+          <t>102837; 138273</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>74231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>78592</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3040; 14895</t>
+          <t>3176; 15355</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6595; 21598</t>
+          <t>6162; 21474</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6279</t>
+          <t>0; 5761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1566; 9880</t>
+          <t>1906; 9943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53027; 86530</t>
+          <t>53156; 85293</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>101774; 145358</t>
+          <t>102326; 145174</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45284; 76005</t>
+          <t>44493; 76547</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>57165; 82538</t>
+          <t>62538; 88749</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60620; 93923</t>
+          <t>60720; 93548</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110552; 155869</t>
+          <t>113514; 159893</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47080; 78563</t>
+          <t>46562; 81196</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>60266; 86464</t>
+          <t>65482; 94262</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165986</t>
+          <t>181734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>243334</t>
+          <t>269983</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>409320</t>
+          <t>451717</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84314; 127878</t>
+          <t>84508; 125005</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>133317; 184393</t>
+          <t>134874; 186879</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97605; 141694</t>
+          <t>97874; 143900</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>127502; 195970</t>
+          <t>158249; 211511</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>139325; 191573</t>
+          <t>140398; 192601</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>298251; 365354</t>
+          <t>296357; 367316</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>167917; 225040</t>
+          <t>167876; 225127</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>198312; 271434</t>
+          <t>245232; 296886</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>236663; 301408</t>
+          <t>237248; 301847</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>447291; 534516</t>
+          <t>445447; 533301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>277983; 348591</t>
+          <t>279448; 354622</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>353231; 454240</t>
+          <t>416065; 484412</t>
         </is>
       </c>
     </row>
